--- a/grupos/5APV - Estadisticos 20211.xlsx
+++ b/grupos/5APV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -206,15 +206,15 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,238 +227,238 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>AULIS</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>JOSMAR ANTONIO</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>CRUZ JESUS</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JOSHUA</t>
+  </si>
+  <si>
+    <t>LUIS ALFREDO</t>
+  </si>
+  <si>
+    <t>ANDREA YAMILET</t>
+  </si>
+  <si>
+    <t>JESUS ARMANDO</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
+    <t>ARRIETA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>AULIS</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
   </si>
   <si>
     <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>JOSMAR ANTONIO</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>CRUZ JESUS</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>JOSHUA</t>
-  </si>
-  <si>
-    <t>LUIS ALFREDO</t>
-  </si>
-  <si>
-    <t>ANDREA YAMILET</t>
-  </si>
-  <si>
-    <t>JESUS ARMANDO</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
   </si>
   <si>
     <t>JESUS ALBERTO</t>
@@ -1013,22 +1013,22 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1049,22 +1049,22 @@
         <v>-1</v>
       </c>
       <c r="T4">
+        <v>7</v>
+      </c>
+      <c r="U4">
+        <v>10</v>
+      </c>
+      <c r="V4">
+        <v>7</v>
+      </c>
+      <c r="W4">
+        <v>9</v>
+      </c>
+      <c r="X4">
+        <v>5</v>
+      </c>
+      <c r="Y4">
         <v>8</v>
-      </c>
-      <c r="U4">
-        <v>10</v>
-      </c>
-      <c r="V4">
-        <v>7</v>
-      </c>
-      <c r="W4">
-        <v>9</v>
-      </c>
-      <c r="X4">
-        <v>5</v>
-      </c>
-      <c r="Y4">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1078,10 +1078,10 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -1090,13 +1090,13 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1105,7 +1105,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1132,16 +1132,16 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1167,22 +1167,22 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1244,22 +1244,22 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1295,7 +1295,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1321,22 +1321,22 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1398,22 +1398,22 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1466,13 +1466,13 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>-1</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1481,7 +1481,7 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1490,7 +1490,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1520,13 +1520,13 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>-1</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1552,22 +1552,22 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1588,7 +1588,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1629,22 +1629,22 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1665,7 +1665,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>10</v>
@@ -1680,7 +1680,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1706,22 +1706,22 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1745,10 +1745,10 @@
         <v>8</v>
       </c>
       <c r="U13">
+        <v>7</v>
+      </c>
+      <c r="V13">
         <v>8</v>
-      </c>
-      <c r="V13">
-        <v>9</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1783,22 +1783,22 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1825,7 +1825,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1860,22 +1860,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1896,13 +1896,13 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>10</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1937,22 +1937,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2005,13 +2005,13 @@
         <v>-1</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>-1</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -2029,7 +2029,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2059,13 +2059,13 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>-1</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2082,13 +2082,13 @@
         <v>-1</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>-1</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2106,7 +2106,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2136,13 +2136,13 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>-1</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2168,22 +2168,22 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2207,19 +2207,19 @@
         <v>8</v>
       </c>
       <c r="U19">
+        <v>9</v>
+      </c>
+      <c r="V19">
         <v>8</v>
       </c>
-      <c r="V19">
-        <v>6</v>
-      </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2245,22 +2245,22 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2296,7 +2296,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2322,22 +2322,22 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2364,16 +2364,16 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2399,22 +2399,22 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2450,7 +2450,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2461,13 +2461,13 @@
         <v>-1</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>-1</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -2479,19 +2479,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2515,19 +2515,19 @@
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>-1</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2553,22 +2553,22 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2598,13 +2598,13 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2618,10 +2618,10 @@
         <v>-1</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F25">
         <v>-1</v>
@@ -2630,7 +2630,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2645,7 +2645,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2672,16 +2672,16 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>-1</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2698,13 +2698,13 @@
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F26">
         <v>-1</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2722,7 +2722,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2752,13 +2752,13 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>-1</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2772,10 +2772,10 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>-1</v>
@@ -2787,10 +2787,10 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2799,7 +2799,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2823,13 +2823,13 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>-1</v>
@@ -2846,13 +2846,13 @@
         <v>5</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F28">
         <v>-1</v>
@@ -2861,22 +2861,22 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2900,19 +2900,19 @@
         <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>-1</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2938,22 +2938,22 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2989,7 +2989,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3018,19 +3018,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3066,7 +3066,7 @@
         <v>-1</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3092,22 +3092,22 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3143,7 +3143,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3169,22 +3169,22 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3205,10 +3205,10 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3220,7 +3220,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3246,22 +3246,22 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3288,7 +3288,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3297,7 +3297,7 @@
         <v>5</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3323,22 +3323,22 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3382,40 +3382,40 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>-1</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F35">
         <v>-1</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H35">
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3436,22 +3436,22 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>-1</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3477,22 +3477,22 @@
         <v>9</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3513,13 +3513,13 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U36">
         <v>6</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3528,7 +3528,7 @@
         <v>-1</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3554,22 +3554,22 @@
         <v>9</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3590,13 +3590,13 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>10</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -3605,7 +3605,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3616,13 +3616,13 @@
         <v>9</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D38">
         <v>5</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F38">
         <v>-1</v>
@@ -3631,22 +3631,22 @@
         <v>7</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L38">
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3667,16 +3667,16 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>5</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>-1</v>
@@ -3708,22 +3708,22 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L39">
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3753,13 +3753,13 @@
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>-1</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3770,37 +3770,37 @@
         <v>-1</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F40">
         <v>-1</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H40">
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3824,19 +3824,19 @@
         <v>-1</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>-1</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3853,7 +3853,7 @@
         <v>6</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F41">
         <v>-1</v>
@@ -3865,19 +3865,19 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L41">
         <v>-1</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3901,13 +3901,13 @@
         <v>5</v>
       </c>
       <c r="U41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X41">
         <v>-1</v>
@@ -4010,25 +4010,25 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>57.89</v>
+        <v>50</v>
       </c>
       <c r="G3">
-        <v>5.26</v>
+        <v>26.32</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>36.84</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4045,27 +4045,27 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>63.16</v>
       </c>
       <c r="G4">
-        <v>13.16</v>
+        <v>15.79</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>23.68</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -4074,30 +4074,30 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>78.95</v>
+      </c>
+      <c r="G5">
+        <v>21.05</v>
+      </c>
+      <c r="H5">
+        <v>7.9</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>65.79000000000001</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I5">
-        <v>13</v>
-      </c>
-      <c r="J5">
-        <v>34.21</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -4106,30 +4106,30 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>81.58</v>
+      </c>
+      <c r="G6">
+        <v>18.42</v>
+      </c>
+      <c r="H6">
+        <v>7.8</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>9.1</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>26.32</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -4138,25 +4138,25 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>84.20999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>15.79</v>
+        <v>13.16</v>
       </c>
     </row>
   </sheetData>
@@ -4166,7 +4166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4195,16 +4195,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920308</v>
+        <v>19330051920311</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4215,56 +4215,56 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920308</v>
+        <v>19330051920312</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
         <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920311</v>
+        <v>19330051920450</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920312</v>
+        <v>19330051920450</v>
       </c>
       <c r="B5" t="s">
         <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -4278,16 +4278,16 @@
         <v>19330051920450</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>64</v>
@@ -4295,393 +4295,393 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920450</v>
+        <v>19330051920319</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920450</v>
+        <v>19330051920327</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920450</v>
+        <v>19330051920327</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920450</v>
+        <v>19330051920327</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920319</v>
+        <v>19330051920327</v>
       </c>
       <c r="B11" t="s">
         <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920327</v>
+        <v>19330051920453</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920327</v>
+        <v>19330051920453</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920327</v>
+        <v>19330051920453</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920327</v>
+        <v>19330051920453</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920327</v>
+        <v>19330051920334</v>
       </c>
       <c r="B16" t="s">
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920327</v>
+        <v>19330051920334</v>
       </c>
       <c r="B17" t="s">
         <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920453</v>
+        <v>19330051920334</v>
       </c>
       <c r="B18" t="s">
         <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920453</v>
+        <v>19330051920338</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
         <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920453</v>
+        <v>19330051920338</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
         <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920453</v>
+        <v>19330051920339</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
         <v>108</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920453</v>
+        <v>19330051920339</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920453</v>
+        <v>19330051920339</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
         <v>108</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920334</v>
+        <v>19330051920339</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
         <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920334</v>
+        <v>19330051920340</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920334</v>
+        <v>19330051920340</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -4695,56 +4695,56 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920334</v>
+        <v>19330051920445</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920334</v>
+        <v>19330051920342</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920338</v>
+        <v>19330051920342</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
@@ -4755,16 +4755,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920338</v>
+        <v>19330051920342</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -4775,116 +4775,116 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920338</v>
+        <v>19330051920347</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920338</v>
+        <v>19330051920347</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920339</v>
+        <v>19330051920350</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>19330051920339</v>
+        <v>19330051920352</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>19330051920339</v>
+        <v>19330051920354</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>19330051920339</v>
+        <v>19330051920354</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -4895,662 +4895,62 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>19330051920339</v>
+        <v>19330051920353</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>19330051920339</v>
+        <v>19330051920353</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D38" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>19330051920340</v>
+        <v>19330051920355</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920340</v>
-      </c>
-      <c r="B40" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" t="s">
-        <v>112</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920340</v>
-      </c>
-      <c r="B41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C41" t="s">
-        <v>95</v>
-      </c>
-      <c r="D41" t="s">
-        <v>112</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920340</v>
-      </c>
-      <c r="B42" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42" t="s">
-        <v>112</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920445</v>
-      </c>
-      <c r="B43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" t="s">
-        <v>74</v>
-      </c>
-      <c r="D43" t="s">
-        <v>113</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920445</v>
-      </c>
-      <c r="B44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" t="s">
-        <v>74</v>
-      </c>
-      <c r="D44" t="s">
-        <v>113</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920445</v>
-      </c>
-      <c r="B45" t="s">
-        <v>79</v>
-      </c>
-      <c r="C45" t="s">
-        <v>74</v>
-      </c>
-      <c r="D45" t="s">
-        <v>113</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920445</v>
-      </c>
-      <c r="B46" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" t="s">
-        <v>74</v>
-      </c>
-      <c r="D46" t="s">
-        <v>113</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920342</v>
-      </c>
-      <c r="B47" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" t="s">
-        <v>114</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920342</v>
-      </c>
-      <c r="B48" t="s">
-        <v>80</v>
-      </c>
-      <c r="C48" t="s">
-        <v>96</v>
-      </c>
-      <c r="D48" t="s">
-        <v>114</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920342</v>
-      </c>
-      <c r="B49" t="s">
-        <v>80</v>
-      </c>
-      <c r="C49" t="s">
-        <v>96</v>
-      </c>
-      <c r="D49" t="s">
-        <v>114</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920347</v>
-      </c>
-      <c r="B50" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" t="s">
-        <v>115</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920347</v>
-      </c>
-      <c r="B51" t="s">
-        <v>81</v>
-      </c>
-      <c r="C51" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51" t="s">
-        <v>115</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920347</v>
-      </c>
-      <c r="B52" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" t="s">
-        <v>97</v>
-      </c>
-      <c r="D52" t="s">
-        <v>115</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920347</v>
-      </c>
-      <c r="B53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" t="s">
-        <v>97</v>
-      </c>
-      <c r="D53" t="s">
-        <v>115</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19330051920347</v>
-      </c>
-      <c r="B54" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" t="s">
-        <v>97</v>
-      </c>
-      <c r="D54" t="s">
-        <v>115</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920347</v>
-      </c>
-      <c r="B55" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" t="s">
-        <v>97</v>
-      </c>
-      <c r="D55" t="s">
-        <v>115</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920350</v>
-      </c>
-      <c r="B56" t="s">
-        <v>82</v>
-      </c>
-      <c r="C56" t="s">
-        <v>98</v>
-      </c>
-      <c r="D56" t="s">
-        <v>116</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920352</v>
-      </c>
-      <c r="B57" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57" t="s">
-        <v>99</v>
-      </c>
-      <c r="D57" t="s">
-        <v>117</v>
-      </c>
-      <c r="E57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920352</v>
-      </c>
-      <c r="B58" t="s">
-        <v>83</v>
-      </c>
-      <c r="C58" t="s">
-        <v>99</v>
-      </c>
-      <c r="D58" t="s">
-        <v>117</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920352</v>
-      </c>
-      <c r="B59" t="s">
-        <v>83</v>
-      </c>
-      <c r="C59" t="s">
-        <v>99</v>
-      </c>
-      <c r="D59" t="s">
-        <v>117</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920354</v>
-      </c>
-      <c r="B60" t="s">
-        <v>84</v>
-      </c>
-      <c r="C60" t="s">
-        <v>100</v>
-      </c>
-      <c r="D60" t="s">
-        <v>118</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920354</v>
-      </c>
-      <c r="B61" t="s">
-        <v>84</v>
-      </c>
-      <c r="C61" t="s">
-        <v>100</v>
-      </c>
-      <c r="D61" t="s">
-        <v>118</v>
-      </c>
-      <c r="E61" t="s">
-        <v>5</v>
-      </c>
-      <c r="F61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920354</v>
-      </c>
-      <c r="B62" t="s">
-        <v>84</v>
-      </c>
-      <c r="C62" t="s">
-        <v>100</v>
-      </c>
-      <c r="D62" t="s">
-        <v>118</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920354</v>
-      </c>
-      <c r="B63" t="s">
-        <v>84</v>
-      </c>
-      <c r="C63" t="s">
-        <v>100</v>
-      </c>
-      <c r="D63" t="s">
-        <v>118</v>
-      </c>
-      <c r="E63" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920354</v>
-      </c>
-      <c r="B64" t="s">
-        <v>84</v>
-      </c>
-      <c r="C64" t="s">
-        <v>100</v>
-      </c>
-      <c r="D64" t="s">
-        <v>118</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920354</v>
-      </c>
-      <c r="B65" t="s">
-        <v>84</v>
-      </c>
-      <c r="C65" t="s">
-        <v>100</v>
-      </c>
-      <c r="D65" t="s">
-        <v>118</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920353</v>
-      </c>
-      <c r="B66" t="s">
-        <v>85</v>
-      </c>
-      <c r="C66" t="s">
-        <v>101</v>
-      </c>
-      <c r="D66" t="s">
-        <v>119</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920353</v>
-      </c>
-      <c r="B67" t="s">
-        <v>85</v>
-      </c>
-      <c r="C67" t="s">
-        <v>101</v>
-      </c>
-      <c r="D67" t="s">
-        <v>119</v>
-      </c>
-      <c r="E67" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920355</v>
-      </c>
-      <c r="B68" t="s">
-        <v>84</v>
-      </c>
-      <c r="C68" t="s">
-        <v>84</v>
-      </c>
-      <c r="D68" t="s">
-        <v>120</v>
-      </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920355</v>
-      </c>
-      <c r="B69" t="s">
-        <v>84</v>
-      </c>
-      <c r="C69" t="s">
-        <v>84</v>
-      </c>
-      <c r="D69" t="s">
-        <v>120</v>
-      </c>
-      <c r="E69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5589,16 +4989,16 @@
         <v>19330051920327</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5606,16 +5006,16 @@
         <v>19330051920453</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5623,109 +5023,109 @@
         <v>19330051920339</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920347</v>
+        <v>19330051920450</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920354</v>
+        <v>19330051920334</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920450</v>
+        <v>19330051920342</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920334</v>
+        <v>19330051920338</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920338</v>
+        <v>19330051920340</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920340</v>
+        <v>19330051920347</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
         <v>95</v>
@@ -5734,123 +5134,123 @@
         <v>112</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920445</v>
+        <v>19330051920354</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920342</v>
+        <v>19330051920353</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920352</v>
+        <v>19330051920311</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920308</v>
+        <v>19330051920312</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
         <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920353</v>
+        <v>19330051920319</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920355</v>
+        <v>19330051920445</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920311</v>
+        <v>19330051920350</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -5858,16 +5258,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920312</v>
+        <v>19330051920352</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5875,16 +5275,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920319</v>
+        <v>19330051920355</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -5892,30 +5292,30 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920350</v>
+        <v>19330051920307</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920307</v>
+        <v>19330051920308</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
         <v>146</v>
@@ -5929,10 +5329,10 @@
         <v>19330051920309</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
         <v>147</v>
@@ -5946,10 +5346,10 @@
         <v>19330051920316</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
         <v>148</v>
@@ -5963,10 +5363,10 @@
         <v>19330051920318</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
         <v>149</v>
@@ -5980,10 +5380,10 @@
         <v>19330051920323</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
         <v>150</v>
@@ -5997,10 +5397,10 @@
         <v>19330051920441</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
         <v>151</v>
@@ -6014,10 +5414,10 @@
         <v>19330051920325</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D27" t="s">
         <v>152</v>
@@ -6031,10 +5431,10 @@
         <v>19330051920321</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D28" t="s">
         <v>153</v>
@@ -6048,10 +5448,10 @@
         <v>19330051920330</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D29" t="s">
         <v>154</v>
@@ -6065,10 +5465,10 @@
         <v>19330051920332</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
         <v>155</v>
@@ -6082,10 +5482,10 @@
         <v>19330051920331</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D31" t="s">
         <v>156</v>
@@ -6099,10 +5499,10 @@
         <v>19330051920333</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
         <v>157</v>
@@ -6116,10 +5516,10 @@
         <v>19330051920337</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s">
         <v>158</v>
@@ -6133,10 +5533,10 @@
         <v>19330051920341</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
         <v>159</v>
@@ -6150,10 +5550,10 @@
         <v>19330051920344</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s">
         <v>160</v>
@@ -6167,10 +5567,10 @@
         <v>19330051920440</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D36" t="s">
         <v>161</v>
@@ -6184,10 +5584,10 @@
         <v>19330051920345</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D37" t="s">
         <v>162</v>
@@ -6201,10 +5601,10 @@
         <v>19330051920346</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D38" t="s">
         <v>163</v>
@@ -6218,13 +5618,13 @@
         <v>19330051920351</v>
       </c>
       <c r="B39" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -6237,7 +5637,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6269,22 +5669,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920307</v>
+        <v>19330051920323</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6292,16 +5692,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920312</v>
+        <v>19330051920323</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -6310,21 +5710,21 @@
         <v>59</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920319</v>
+        <v>19330051920352</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -6333,21 +5733,21 @@
         <v>60</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920323</v>
+        <v>19330051920352</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -6356,21 +5756,21 @@
         <v>59</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920321</v>
+        <v>19330051920307</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -6384,16 +5784,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920345</v>
+        <v>19330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -6402,30 +5802,76 @@
         <v>59</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920350</v>
+        <v>19330051920319</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920321</v>
+      </c>
+      <c r="B9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
         <v>59</v>
       </c>
-      <c r="G8">
-        <v>-1</v>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920345</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5APV - Estadisticos 20211.xlsx
+++ b/grupos/5APV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -230,133 +230,277 @@
     <t>BELLO</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>AULIS</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>JOSMAR ANTONIO</t>
+  </si>
+  <si>
+    <t>CRUZ JESUS</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JOSHUA</t>
+  </si>
+  <si>
+    <t>ANDREA YAMILET</t>
+  </si>
+  <si>
+    <t>JESUS ARMANDO</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
     <t>CARDENAS</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
   </si>
   <si>
     <t>PACHECO</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
+    <t>PATIÑO</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
   </si>
   <si>
     <t>AMADOR</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>AULIS</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>BAEZ</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>JOSMAR ANTONIO</t>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ALBERTO</t>
   </si>
   <si>
     <t>KEVIN HONAM</t>
   </si>
   <si>
-    <t>CRUZ JESUS</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>JOSHUA</t>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>SAUL ESTEBAN</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ABRAHAM</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>LUZ ABRIL</t>
+  </si>
+  <si>
+    <t>VICTOR YAHIR</t>
   </si>
   <si>
     <t>LUIS ALFREDO</t>
   </si>
   <si>
-    <t>ANDREA YAMILET</t>
-  </si>
-  <si>
-    <t>JESUS ARMANDO</t>
+    <t>CRISTOPHER ENRIQUE</t>
+  </si>
+  <si>
+    <t>CARLOS FERNANDO</t>
+  </si>
+  <si>
+    <t>CIELO IVETTE</t>
+  </si>
+  <si>
+    <t>GWINETH</t>
+  </si>
+  <si>
+    <t>YOSEF OMAR</t>
   </si>
   <si>
     <t>ABIGAIL</t>
@@ -365,151 +509,7 @@
     <t>ADAN</t>
   </si>
   <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>HERSON ELIAS</t>
-  </si>
-  <si>
     <t>JOEL</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ALBERTO</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>SAUL ESTEBAN</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>LUZ ABRIL</t>
-  </si>
-  <si>
-    <t>VICTOR YAHIR</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ENRIQUE</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>CIELO IVETTE</t>
-  </si>
-  <si>
-    <t>GWINETH</t>
-  </si>
-  <si>
-    <t>YOSEF OMAR</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1025,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>8</v>
@@ -1102,7 +1102,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -1179,7 +1179,7 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -1215,7 +1215,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1256,7 +1256,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -1315,7 +1315,7 @@
         <v>9</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>9</v>
@@ -1333,7 +1333,7 @@
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -1369,7 +1369,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1410,7 +1410,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -1446,7 +1446,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1469,7 +1469,7 @@
         <v>5</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1487,7 +1487,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -1523,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1564,7 +1564,7 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1600,7 +1600,7 @@
         <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1641,7 +1641,7 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1718,7 +1718,7 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -1795,7 +1795,7 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>6</v>
@@ -1872,7 +1872,7 @@
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -1949,7 +1949,7 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -2008,7 +2008,7 @@
         <v>5</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -2026,7 +2026,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -2062,7 +2062,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -2085,7 +2085,7 @@
         <v>5</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -2103,7 +2103,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -2139,7 +2139,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2180,7 +2180,7 @@
         <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -2216,7 +2216,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2257,7 +2257,7 @@
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2334,7 +2334,7 @@
         <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>6</v>
@@ -2370,7 +2370,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2411,7 +2411,7 @@
         <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2470,7 +2470,7 @@
         <v>7</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>6</v>
@@ -2488,7 +2488,7 @@
         <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2524,7 +2524,7 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2565,7 +2565,7 @@
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -2601,7 +2601,7 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2624,7 +2624,7 @@
         <v>5</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -2642,7 +2642,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>5</v>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2701,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -2719,7 +2719,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>5</v>
@@ -2755,7 +2755,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2778,7 +2778,7 @@
         <v>5</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G27">
         <v>7</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>6</v>
@@ -2832,7 +2832,7 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2855,7 +2855,7 @@
         <v>7</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>8</v>
@@ -2873,7 +2873,7 @@
         <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>6</v>
@@ -2909,7 +2909,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2950,7 +2950,7 @@
         <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -2986,7 +2986,7 @@
         <v>10</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -3009,7 +3009,7 @@
         <v>6</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G30">
         <v>8</v>
@@ -3027,7 +3027,7 @@
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>5</v>
@@ -3063,7 +3063,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3104,7 +3104,7 @@
         <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>9</v>
@@ -3181,7 +3181,7 @@
         <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -3217,7 +3217,7 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3258,7 +3258,7 @@
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3335,7 +3335,7 @@
         <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>10</v>
@@ -3394,7 +3394,7 @@
         <v>7</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -3412,7 +3412,7 @@
         <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>5</v>
@@ -3448,7 +3448,7 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3471,7 +3471,7 @@
         <v>7</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <v>9</v>
@@ -3489,7 +3489,7 @@
         <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <v>7</v>
@@ -3525,7 +3525,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -3566,7 +3566,7 @@
         <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>10</v>
@@ -3602,7 +3602,7 @@
         <v>9</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y37">
         <v>10</v>
@@ -3625,7 +3625,7 @@
         <v>6</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G38">
         <v>7</v>
@@ -3643,7 +3643,7 @@
         <v>7</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M38">
         <v>6</v>
@@ -3679,7 +3679,7 @@
         <v>7</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y38">
         <v>7</v>
@@ -3702,7 +3702,7 @@
         <v>8</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G39">
         <v>8</v>
@@ -3720,7 +3720,7 @@
         <v>6</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
         <v>5</v>
@@ -3756,7 +3756,7 @@
         <v>7</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y39">
         <v>7</v>
@@ -3779,7 +3779,7 @@
         <v>7</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -3797,7 +3797,7 @@
         <v>7</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>5</v>
@@ -3833,7 +3833,7 @@
         <v>7</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -3856,7 +3856,7 @@
         <v>7</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G41">
         <v>6</v>
@@ -3874,7 +3874,7 @@
         <v>7</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>6</v>
@@ -3910,7 +3910,7 @@
         <v>7</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y41">
         <v>6</v>
@@ -3978,25 +3978,25 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>42.11</v>
+        <v>31.58</v>
       </c>
       <c r="G2">
-        <v>15.79</v>
+        <v>68.42</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>42.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4166,7 +4166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4201,10 +4201,10 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4215,22 +4215,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920312</v>
+        <v>19330051920450</v>
       </c>
       <c r="B3" t="s">
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4238,73 +4238,73 @@
         <v>19330051920450</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920450</v>
+        <v>19330051920319</v>
       </c>
       <c r="B5" t="s">
         <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920450</v>
+        <v>19330051920327</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920319</v>
+        <v>19330051920327</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -4318,73 +4318,73 @@
         <v>19330051920327</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920327</v>
+        <v>19330051920453</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920327</v>
+        <v>19330051920453</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920327</v>
+        <v>19330051920453</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -4395,16 +4395,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920453</v>
+        <v>19330051920334</v>
       </c>
       <c r="B12" t="s">
         <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -4415,16 +4415,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920453</v>
+        <v>19330051920334</v>
       </c>
       <c r="B13" t="s">
         <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -4435,522 +4435,202 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920453</v>
+        <v>19330051920338</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920453</v>
+        <v>19330051920339</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920334</v>
+        <v>19330051920339</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920334</v>
+        <v>19330051920339</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920334</v>
+        <v>19330051920340</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920338</v>
+        <v>19330051920342</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920338</v>
+        <v>19330051920342</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920339</v>
+        <v>19330051920347</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920339</v>
+        <v>19330051920354</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920339</v>
+        <v>19330051920353</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
         <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920339</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920340</v>
-      </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920340</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920445</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920342</v>
-      </c>
-      <c r="B28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" t="s">
-        <v>111</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920342</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920342</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920347</v>
-      </c>
-      <c r="B31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" t="s">
-        <v>112</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920347</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920350</v>
-      </c>
-      <c r="B33" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>96</v>
-      </c>
-      <c r="D33" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920352</v>
-      </c>
-      <c r="B34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920354</v>
-      </c>
-      <c r="B35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" t="s">
-        <v>115</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920354</v>
-      </c>
-      <c r="B36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" t="s">
-        <v>115</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920353</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" t="s">
-        <v>116</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920353</v>
-      </c>
-      <c r="B38" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" t="s">
-        <v>99</v>
-      </c>
-      <c r="D38" t="s">
-        <v>116</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920355</v>
-      </c>
-      <c r="B39" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" t="s">
-        <v>83</v>
-      </c>
-      <c r="D39" t="s">
-        <v>117</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4989,16 +4669,16 @@
         <v>19330051920327</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5006,16 +4686,16 @@
         <v>19330051920453</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5023,16 +4703,16 @@
         <v>19330051920339</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5040,16 +4720,16 @@
         <v>19330051920450</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5057,16 +4737,16 @@
         <v>19330051920334</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5074,115 +4754,115 @@
         <v>19330051920342</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920338</v>
+        <v>19330051920311</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920340</v>
+        <v>19330051920319</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920347</v>
+        <v>19330051920338</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920354</v>
+        <v>19330051920340</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920353</v>
+        <v>19330051920347</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920311</v>
+        <v>19330051920354</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5190,16 +4870,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920312</v>
+        <v>19330051920353</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5207,98 +4887,98 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920319</v>
+        <v>19330051920307</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920445</v>
+        <v>19330051920308</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920350</v>
+        <v>19330051920309</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920352</v>
+        <v>19330051920312</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920355</v>
+        <v>19330051920316</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920307</v>
+        <v>19330051920318</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
         <v>145</v>
@@ -5309,13 +4989,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920308</v>
+        <v>19330051920323</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
         <v>146</v>
@@ -5326,13 +5006,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920309</v>
+        <v>19330051920441</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D22" t="s">
         <v>147</v>
@@ -5343,13 +5023,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920316</v>
+        <v>19330051920325</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="D23" t="s">
         <v>148</v>
@@ -5360,13 +5040,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920318</v>
+        <v>19330051920321</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
         <v>149</v>
@@ -5377,13 +5057,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920323</v>
+        <v>19330051920330</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
         <v>150</v>
@@ -5394,13 +5074,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920441</v>
+        <v>19330051920332</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
         <v>151</v>
@@ -5411,13 +5091,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920325</v>
+        <v>19330051920331</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D27" t="s">
         <v>152</v>
@@ -5428,13 +5108,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920321</v>
+        <v>19330051920333</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
         <v>153</v>
@@ -5445,13 +5125,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920330</v>
+        <v>19330051920337</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
         <v>154</v>
@@ -5462,13 +5142,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920332</v>
+        <v>19330051920445</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
         <v>155</v>
@@ -5479,13 +5159,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920331</v>
+        <v>19330051920341</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
         <v>156</v>
@@ -5496,13 +5176,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920333</v>
+        <v>19330051920344</v>
       </c>
       <c r="B32" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
         <v>157</v>
@@ -5513,13 +5193,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920337</v>
+        <v>19330051920440</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
         <v>158</v>
@@ -5530,13 +5210,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920341</v>
+        <v>19330051920345</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
         <v>159</v>
@@ -5547,13 +5227,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920344</v>
+        <v>19330051920346</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D35" t="s">
         <v>160</v>
@@ -5564,13 +5244,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920440</v>
+        <v>19330051920350</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
         <v>161</v>
@@ -5581,16 +5261,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>19330051920345</v>
+        <v>19330051920351</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5598,16 +5278,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>19330051920346</v>
+        <v>19330051920352</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="C38" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -5615,16 +5295,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>19330051920351</v>
+        <v>19330051920355</v>
       </c>
       <c r="B39" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="C39" t="s">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5637,7 +5317,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5672,13 +5352,13 @@
         <v>19330051920323</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5695,13 +5375,13 @@
         <v>19330051920323</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5718,13 +5398,13 @@
         <v>19330051920352</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5741,13 +5421,13 @@
         <v>19330051920352</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5756,7 +5436,7 @@
         <v>59</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -5764,13 +5444,13 @@
         <v>19330051920307</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -5787,13 +5467,13 @@
         <v>19330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5802,67 +5482,67 @@
         <v>59</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920319</v>
+        <v>19330051920316</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920321</v>
+        <v>19330051920319</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920345</v>
+        <v>19330051920321</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -5871,6 +5551,98 @@
         <v>59</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920330</v>
+      </c>
+      <c r="B11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920337</v>
+      </c>
+      <c r="B12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920345</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920351</v>
+      </c>
+      <c r="B14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APV - Estadisticos 20211.xlsx
+++ b/grupos/5APV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -2458,7 +2458,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -2512,7 +2512,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -4042,25 +4042,25 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4">
-        <v>63.16</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="G4">
         <v>15.79</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>21.05</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4166,7 +4166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4407,50 +4407,50 @@
         <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920334</v>
+        <v>19330051920338</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920338</v>
+        <v>19330051920339</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4467,10 +4467,10 @@
         <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4487,44 +4487,44 @@
         <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920339</v>
+        <v>19330051920340</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920340</v>
+        <v>19330051920342</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -4547,24 +4547,24 @@
         <v>102</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920342</v>
+        <v>19330051920347</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -4575,61 +4575,41 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920347</v>
+        <v>19330051920354</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920354</v>
+        <v>19330051920353</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920353</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4734,16 +4714,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920334</v>
+        <v>19330051920342</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4751,33 +4731,33 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920342</v>
+        <v>19330051920311</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920311</v>
+        <v>19330051920319</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4785,16 +4765,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920319</v>
+        <v>19330051920334</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E9">
         <v>1</v>

--- a/grupos/5APV - Estadisticos 20211.xlsx
+++ b/grupos/5APV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -233,229 +233,229 @@
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>JOSMAR ANTONIO</t>
+  </si>
+  <si>
+    <t>CRUZ JESUS</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JOSHUA</t>
+  </si>
+  <si>
+    <t>ANDREA YAMILET</t>
+  </si>
+  <si>
+    <t>JESUS ARMANDO</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>AULIS</t>
   </si>
   <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>JOSMAR ANTONIO</t>
-  </si>
-  <si>
-    <t>CRUZ JESUS</t>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ALBERTO</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>SAUL ESTEBAN</t>
   </si>
   <si>
     <t>ALDO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>JOSHUA</t>
-  </si>
-  <si>
-    <t>ANDREA YAMILET</t>
-  </si>
-  <si>
-    <t>JESUS ARMANDO</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ALBERTO</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>SAUL ESTEBAN</t>
   </si>
   <si>
     <t>ADRIAN</t>
@@ -1617,7 +1617,7 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -1635,7 +1635,7 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -1671,7 +1671,7 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -4010,13 +4010,13 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>10</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="G3">
         <v>26.32</v>
@@ -4025,10 +4025,10 @@
         <v>7.6</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>23.68</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4166,7 +4166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4201,10 +4201,10 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4221,10 +4221,10 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -4241,10 +4241,10 @@
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920319</v>
+        <v>19330051920327</v>
       </c>
       <c r="B5" t="s">
         <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4278,19 +4278,19 @@
         <v>19330051920327</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4298,39 +4298,39 @@
         <v>19330051920327</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920327</v>
+        <v>19330051920453</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4338,19 +4338,19 @@
         <v>19330051920453</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4358,79 +4358,79 @@
         <v>19330051920453</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920453</v>
+        <v>19330051920334</v>
       </c>
       <c r="B11" t="s">
         <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920334</v>
+        <v>19330051920338</v>
       </c>
       <c r="B12" t="s">
         <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920338</v>
+        <v>19330051920339</v>
       </c>
       <c r="B13" t="s">
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4438,19 +4438,19 @@
         <v>19330051920339</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4458,53 +4458,53 @@
         <v>19330051920339</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920339</v>
+        <v>19330051920340</v>
       </c>
       <c r="B16" t="s">
         <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920340</v>
+        <v>19330051920342</v>
       </c>
       <c r="B17" t="s">
         <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
@@ -4518,33 +4518,33 @@
         <v>19330051920342</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920342</v>
+        <v>19330051920347</v>
       </c>
       <c r="B19" t="s">
         <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -4555,61 +4555,41 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920347</v>
+        <v>19330051920354</v>
       </c>
       <c r="B20" t="s">
         <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920354</v>
+        <v>19330051920353</v>
       </c>
       <c r="B21" t="s">
         <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920353</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4649,13 +4629,13 @@
         <v>19330051920327</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4666,13 +4646,13 @@
         <v>19330051920453</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -4683,13 +4663,13 @@
         <v>19330051920339</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -4703,10 +4683,10 @@
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4717,13 +4697,13 @@
         <v>19330051920342</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4737,10 +4717,10 @@
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4748,10 +4728,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920319</v>
+        <v>19330051920334</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
         <v>83</v>
@@ -4765,16 +4745,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920334</v>
+        <v>19330051920338</v>
       </c>
       <c r="B9" t="s">
         <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4782,16 +4762,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920338</v>
+        <v>19330051920340</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
         <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4799,16 +4779,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920340</v>
+        <v>19330051920347</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
         <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4816,16 +4796,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920347</v>
+        <v>19330051920354</v>
       </c>
       <c r="B12" t="s">
         <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4833,16 +4813,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920354</v>
+        <v>19330051920353</v>
       </c>
       <c r="B13" t="s">
         <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4850,30 +4830,30 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920353</v>
+        <v>19330051920307</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920307</v>
+        <v>19330051920308</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
         <v>140</v>
@@ -4884,13 +4864,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920308</v>
+        <v>19330051920309</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
         <v>141</v>
@@ -4901,13 +4881,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920309</v>
+        <v>19330051920312</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
         <v>142</v>
@@ -4918,13 +4898,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920312</v>
+        <v>19330051920316</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>143</v>
@@ -4935,13 +4915,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920316</v>
+        <v>19330051920318</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
         <v>144</v>
@@ -4952,13 +4932,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920318</v>
+        <v>19330051920319</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D20" t="s">
         <v>145</v>
@@ -4972,10 +4952,10 @@
         <v>19330051920323</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D21" t="s">
         <v>146</v>
@@ -4989,10 +4969,10 @@
         <v>19330051920441</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
         <v>147</v>
@@ -5006,10 +4986,10 @@
         <v>19330051920325</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
         <v>148</v>
@@ -5023,10 +5003,10 @@
         <v>19330051920321</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
         <v>149</v>
@@ -5040,10 +5020,10 @@
         <v>19330051920330</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
         <v>150</v>
@@ -5057,10 +5037,10 @@
         <v>19330051920332</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
         <v>151</v>
@@ -5074,10 +5054,10 @@
         <v>19330051920331</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
         <v>152</v>
@@ -5091,10 +5071,10 @@
         <v>19330051920333</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
         <v>153</v>
@@ -5108,10 +5088,10 @@
         <v>19330051920337</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
         <v>154</v>
@@ -5125,10 +5105,10 @@
         <v>19330051920445</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
         <v>155</v>
@@ -5142,10 +5122,10 @@
         <v>19330051920341</v>
       </c>
       <c r="B31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" t="s">
         <v>120</v>
-      </c>
-      <c r="C31" t="s">
-        <v>122</v>
       </c>
       <c r="D31" t="s">
         <v>156</v>
@@ -5159,10 +5139,10 @@
         <v>19330051920344</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s">
         <v>157</v>
@@ -5176,10 +5156,10 @@
         <v>19330051920440</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D33" t="s">
         <v>158</v>
@@ -5193,10 +5173,10 @@
         <v>19330051920345</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
         <v>159</v>
@@ -5210,10 +5190,10 @@
         <v>19330051920346</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
         <v>160</v>
@@ -5227,10 +5207,10 @@
         <v>19330051920350</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D36" t="s">
         <v>161</v>
@@ -5244,13 +5224,13 @@
         <v>19330051920351</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5261,10 +5241,10 @@
         <v>19330051920352</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
         <v>162</v>
@@ -5278,10 +5258,10 @@
         <v>19330051920355</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
         <v>163</v>
@@ -5297,7 +5277,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5332,10 +5312,10 @@
         <v>19330051920323</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
         <v>146</v>
@@ -5355,10 +5335,10 @@
         <v>19330051920323</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D3" t="s">
         <v>146</v>
@@ -5378,10 +5358,10 @@
         <v>19330051920352</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
         <v>162</v>
@@ -5401,10 +5381,10 @@
         <v>19330051920352</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
         <v>162</v>
@@ -5424,13 +5404,13 @@
         <v>19330051920307</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -5447,13 +5427,13 @@
         <v>19330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5470,13 +5450,13 @@
         <v>19330051920316</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -5490,39 +5470,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920319</v>
+        <v>19330051920321</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920321</v>
+        <v>19330051920330</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
         <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -5536,16 +5516,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920330</v>
+        <v>19330051920337</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -5559,16 +5539,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920337</v>
+        <v>19330051920345</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -5582,16 +5562,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920345</v>
+        <v>19330051920351</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -5600,29 +5580,6 @@
         <v>59</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920351</v>
-      </c>
-      <c r="B14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APV - Estadisticos 20211.xlsx
+++ b/grupos/5APV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -206,15 +206,15 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
+    <t>Sánchez Sánchez Miguel</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,18 +227,63 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
     <t>BELLO</t>
   </si>
   <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
@@ -248,28 +293,82 @@
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>SANDOVAL</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>XOLIO</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
     <t>ARENAS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>AULIS</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
   </si>
   <si>
     <t>TIBURCIO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>GOMEZ</t>
@@ -278,36 +377,93 @@
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>MONTERROSAS</t>
   </si>
   <si>
     <t>CAMPOS</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ALBERTO</t>
+  </si>
+  <si>
     <t>JOSMAR ANTONIO</t>
   </si>
   <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
     <t>CRUZ JESUS</t>
   </si>
   <si>
+    <t>SAUL ESTEBAN</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ABRAHAM</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
     <t>EDGAR</t>
   </si>
   <si>
     <t>JAVIER</t>
   </si>
   <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>LUZ ABRIL</t>
+  </si>
+  <si>
     <t>GABRIELA</t>
   </si>
   <si>
+    <t>VICTOR YAHIR</t>
+  </si>
+  <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
@@ -317,196 +473,40 @@
     <t>JOSHUA</t>
   </si>
   <si>
+    <t>LUIS ALFREDO</t>
+  </si>
+  <si>
     <t>ANDREA YAMILET</t>
   </si>
   <si>
+    <t>CRISTOPHER ENRIQUE</t>
+  </si>
+  <si>
+    <t>CARLOS FERNANDO</t>
+  </si>
+  <si>
     <t>JESUS ARMANDO</t>
   </si>
   <si>
+    <t>CIELO IVETTE</t>
+  </si>
+  <si>
+    <t>GWINETH</t>
+  </si>
+  <si>
+    <t>YOSEF OMAR</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
     <t>MISAEL</t>
   </si>
   <si>
     <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>AULIS</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ALBERTO</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>SAUL ESTEBAN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>LUZ ABRIL</t>
-  </si>
-  <si>
-    <t>VICTOR YAHIR</t>
-  </si>
-  <si>
-    <t>LUIS ALFREDO</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ENRIQUE</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>CIELO IVETTE</t>
-  </si>
-  <si>
-    <t>GWINETH</t>
-  </si>
-  <si>
-    <t>YOSEF OMAR</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>ADAN</t>
   </si>
   <si>
     <t>JOEL</t>
@@ -1031,34 +1031,34 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>7</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>7</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -1099,7 +1099,7 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -1108,22 +1108,22 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -1135,7 +1135,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -1185,28 +1185,28 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>9</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1232,7 +1232,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>7</v>
@@ -1250,7 +1250,7 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>7</v>
@@ -1262,22 +1262,22 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1286,7 +1286,7 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1327,7 +1327,7 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>8</v>
@@ -1339,34 +1339,34 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1416,37 +1416,37 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>10</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1457,10 +1457,10 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1475,16 +1475,16 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -1493,28 +1493,28 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1526,7 +1526,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1558,7 +1558,7 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -1570,22 +1570,22 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1594,7 +1594,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1647,28 +1647,28 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1724,34 +1724,34 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>7</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1801,34 +1801,34 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>5</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1878,25 +1878,25 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1955,22 +1955,22 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1996,13 +1996,13 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -2014,16 +2014,16 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -2032,31 +2032,31 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2065,7 +2065,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2073,13 +2073,13 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>5</v>
@@ -2091,16 +2091,16 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -2109,31 +2109,31 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2142,7 +2142,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2186,40 +2186,40 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>9</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2263,31 +2263,31 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>10</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2296,7 +2296,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2340,37 +2340,37 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2417,22 +2417,22 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2464,7 +2464,7 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>7</v>
@@ -2476,13 +2476,13 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>7</v>
@@ -2494,31 +2494,31 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2527,7 +2527,7 @@
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2571,37 +2571,37 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>6</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2615,7 +2615,7 @@
         <v>7</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -2633,13 +2633,13 @@
         <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -2648,40 +2648,40 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2689,13 +2689,13 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -2707,16 +2707,16 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -2725,31 +2725,31 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>5</v>
@@ -2758,7 +2758,7 @@
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2766,7 +2766,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>10</v>
@@ -2784,7 +2784,7 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>6</v>
@@ -2793,7 +2793,7 @@
         <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -2802,40 +2802,40 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>5</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2879,34 +2879,34 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>5</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>5</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2956,22 +2956,22 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2997,13 +2997,13 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>6</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>6</v>
@@ -3015,13 +3015,13 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>6</v>
@@ -3033,31 +3033,31 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -3066,7 +3066,7 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3110,28 +3110,28 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3140,7 +3140,7 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3175,7 +3175,7 @@
         <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
         <v>10</v>
@@ -3187,37 +3187,37 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3264,22 +3264,22 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3288,13 +3288,13 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>10</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3341,22 +3341,22 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3388,7 +3388,7 @@
         <v>6</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>7</v>
@@ -3400,13 +3400,13 @@
         <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I35">
         <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
         <v>6</v>
@@ -3418,40 +3418,40 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>6</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3495,22 +3495,22 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>5</v>
@@ -3522,7 +3522,7 @@
         <v>5</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X36">
         <v>5</v>
@@ -3572,25 +3572,25 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U37">
         <v>10</v>
@@ -3649,25 +3649,25 @@
         <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U38">
         <v>6</v>
@@ -3676,10 +3676,10 @@
         <v>5</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>7</v>
@@ -3696,7 +3696,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>8</v>
@@ -3714,7 +3714,7 @@
         <v>6</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
         <v>6</v>
@@ -3726,40 +3726,40 @@
         <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T39">
         <v>5</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X39">
         <v>5</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3767,7 +3767,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -3785,7 +3785,7 @@
         <v>5</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>6</v>
@@ -3803,25 +3803,25 @@
         <v>5</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -3830,13 +3830,13 @@
         <v>5</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X40">
         <v>5</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3862,7 +3862,7 @@
         <v>6</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I41">
         <v>9</v>
@@ -3880,22 +3880,22 @@
         <v>6</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T41">
         <v>5</v>
@@ -3907,7 +3907,7 @@
         <v>5</v>
       </c>
       <c r="W41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X41">
         <v>5</v>
@@ -3978,19 +3978,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>31.58</v>
+        <v>44.74</v>
       </c>
       <c r="G2">
-        <v>68.42</v>
+        <v>55.26</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4010,25 +4010,25 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>52.63</v>
+        <v>55.26</v>
       </c>
       <c r="G3">
-        <v>26.32</v>
+        <v>44.74</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4042,30 +4042,30 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>65.79000000000001</v>
+        <v>60.53</v>
       </c>
       <c r="G4">
-        <v>15.79</v>
+        <v>39.47</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>18.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -4074,16 +4074,16 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="G5">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
       <c r="H5">
         <v>7.9</v>
@@ -4106,16 +4106,16 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>81.58</v>
+        <v>89.47</v>
       </c>
       <c r="G6">
-        <v>18.42</v>
+        <v>10.53</v>
       </c>
       <c r="H6">
         <v>7.8</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -4138,25 +4138,25 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>86.84</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>13.16</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4166,7 +4166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4191,406 +4191,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920311</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920450</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920450</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920327</v>
-      </c>
-      <c r="B5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920327</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920327</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920453</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920453</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920453</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920334</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920338</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920339</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920339</v>
-      </c>
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920339</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920340</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920342</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920342</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920347</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920354</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920353</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4626,217 +4226,217 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920327</v>
+        <v>19330051920307</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920453</v>
+        <v>19330051920308</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920339</v>
+        <v>19330051920309</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920450</v>
+        <v>19330051920311</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920342</v>
+        <v>19330051920312</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920311</v>
+        <v>19330051920316</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
         <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920334</v>
+        <v>19330051920450</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920338</v>
+        <v>19330051920318</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920340</v>
+        <v>19330051920319</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920347</v>
+        <v>19330051920323</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920354</v>
+        <v>19330051920441</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920353</v>
+        <v>19330051920325</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920307</v>
+        <v>19330051920327</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
         <v>139</v>
@@ -4847,13 +4447,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920308</v>
+        <v>19330051920453</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
         <v>140</v>
@@ -4864,13 +4464,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920309</v>
+        <v>19330051920321</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
         <v>141</v>
@@ -4881,13 +4481,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920312</v>
+        <v>19330051920330</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
         <v>142</v>
@@ -4898,13 +4498,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920316</v>
+        <v>19330051920332</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>143</v>
@@ -4915,13 +4515,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920318</v>
+        <v>19330051920331</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
         <v>144</v>
@@ -4932,13 +4532,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920319</v>
+        <v>19330051920333</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
         <v>145</v>
@@ -4949,13 +4549,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920323</v>
+        <v>19330051920334</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
         <v>146</v>
@@ -4966,13 +4566,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920441</v>
+        <v>19330051920337</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
         <v>147</v>
@@ -4983,13 +4583,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920325</v>
+        <v>19330051920338</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
         <v>148</v>
@@ -5000,13 +4600,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920321</v>
+        <v>19330051920339</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
         <v>149</v>
@@ -5017,13 +4617,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920330</v>
+        <v>19330051920340</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
         <v>150</v>
@@ -5034,13 +4634,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920332</v>
+        <v>19330051920445</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
         <v>151</v>
@@ -5051,13 +4651,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920331</v>
+        <v>19330051920342</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s">
         <v>152</v>
@@ -5068,13 +4668,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920333</v>
+        <v>19330051920341</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s">
         <v>153</v>
@@ -5085,13 +4685,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920337</v>
+        <v>19330051920344</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
         <v>154</v>
@@ -5102,13 +4702,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920445</v>
+        <v>19330051920347</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
         <v>155</v>
@@ -5119,13 +4719,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920341</v>
+        <v>19330051920440</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
         <v>156</v>
@@ -5136,13 +4736,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920344</v>
+        <v>19330051920345</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
         <v>157</v>
@@ -5153,13 +4753,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920440</v>
+        <v>19330051920346</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
         <v>158</v>
@@ -5170,13 +4770,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920345</v>
+        <v>19330051920350</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
         <v>159</v>
@@ -5187,16 +4787,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920346</v>
+        <v>19330051920351</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5204,16 +4804,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920350</v>
+        <v>19330051920352</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5221,16 +4821,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>19330051920351</v>
+        <v>19330051920354</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5238,13 +4838,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>19330051920352</v>
+        <v>19330051920353</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D38" t="s">
         <v>162</v>
@@ -5258,10 +4858,10 @@
         <v>19330051920355</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
         <v>163</v>
@@ -5277,7 +4877,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5312,13 +4912,13 @@
         <v>19330051920323</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5335,13 +4935,13 @@
         <v>19330051920323</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5355,22 +4955,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920352</v>
+        <v>19330051920307</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5378,16 +4978,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920352</v>
+        <v>19330051920312</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5401,16 +5001,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920307</v>
+        <v>19330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -5424,16 +5024,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920312</v>
+        <v>19330051920338</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5447,16 +5047,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920316</v>
+        <v>19330051920351</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -5470,116 +5070,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920321</v>
+        <v>19330051920352</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920330</v>
-      </c>
-      <c r="B10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920337</v>
-      </c>
-      <c r="B11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D11" t="s">
-        <v>154</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920345</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920351</v>
-      </c>
-      <c r="B13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>
